--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_los_rios.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:27</t>
+    <t xml:space="preserve">2026-09-09 20:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_los_rios.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_los_rios.xlsx
@@ -24,42 +24,42 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Valdivia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Corral</t>
   </si>
   <si>
+    <t xml:space="preserve">Lanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariquina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paillaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unión</t>
+  </si>
+  <si>
     <t xml:space="preserve">Futrono</t>
   </si>
   <si>
-    <t xml:space="preserve">La Unión</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lago Ranco</t>
   </si>
   <si>
-    <t xml:space="preserve">Lanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Lagos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Máfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariquina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paillaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">Río Bueno</t>
   </si>
   <si>
-    <t xml:space="preserve">Valdivia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:26</t>
+    <t xml:space="preserve">2026-09-18 10:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>73.48</v>
+        <v>76.24</v>
       </c>
     </row>
     <row r="3">
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>70.56</v>
+        <v>73.48</v>
       </c>
     </row>
     <row r="4">
@@ -497,7 +497,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>76.08</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>72.9</v>
+        <v>72.41</v>
       </c>
     </row>
     <row r="6">
@@ -513,7 +513,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>74.94</v>
+        <v>75.34</v>
       </c>
     </row>
     <row r="7">
@@ -521,7 +521,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>72.41</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="8">
@@ -529,7 +529,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>75.34</v>
+        <v>75.4</v>
       </c>
     </row>
     <row r="9">
@@ -537,7 +537,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>73.59</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>75.4</v>
+        <v>76.08</v>
       </c>
     </row>
     <row r="11">
@@ -553,7 +553,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>71.8</v>
+        <v>70.56</v>
       </c>
     </row>
     <row r="12">
@@ -561,7 +561,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>75.19</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="13">
@@ -569,7 +569,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>76.24</v>
+        <v>75.19</v>
       </c>
     </row>
   </sheetData>
